--- a/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-13543_Double_Rounding_Precision.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-13543_Double_Rounding_Precision.xlsx
@@ -8,9 +8,19 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>=1 / 3 * 3</t>
+  </si>
+  <si>
+    <t>=9 / 35 * 7</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -429,100 +439,96 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="9">
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="inlineStr" s="0">
         <is>
           <t>Spreadsheet SpreadsheetResult mySpr()</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="inlineStr" s="0">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="inlineStr" s="0">
         <is>
           <t>Result</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="inlineStr" s="0">
         <is>
           <t>num1</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>=1.73*12</t>
-        </is>
+      <c r="E11" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="inlineStr" s="0">
         <is>
           <t>num2</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>=round(1240.32/1144.9, 5)-1</t>
-        </is>
+      <c r="E12" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="inlineStr" s="0">
         <is>
           <t>Test mySpr mySprTest</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="D18" t="inlineStr">
+      <c r="D18" t="inlineStr" s="0">
         <is>
           <t>_description_</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="inlineStr" s="0">
         <is>
           <t>_res_.$num1</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" t="inlineStr" s="0">
         <is>
           <t>_res_.$num2 (5)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="D19" t="inlineStr">
+      <c r="D19" t="inlineStr" s="0">
         <is>
           <t>_description_</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="inlineStr" s="0">
         <is>
           <t>_res_.$num1</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="inlineStr" s="0">
         <is>
           <t>_res_.$num2 (5)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="inlineStr" s="0">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>20.76</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.08334</v>
+      <c r="E20" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F20" t="n" s="0">
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
